--- a/Config/Excels/Local/L-Localization-成就.xlsx
+++ b/Config/Excels/Local/L-Localization-成就.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24645" windowHeight="11610" tabRatio="671"/>
+    <workbookView windowHeight="18450" tabRatio="671"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48">
   <si>
     <t>##var</t>
   </si>
@@ -25,6 +25,9 @@
     <t>key</t>
   </si>
   <si>
+    <t>is_code</t>
+  </si>
+  <si>
     <t>ChineseSimplified</t>
   </si>
   <si>
@@ -73,10 +76,16 @@
     <t>string</t>
   </si>
   <si>
+    <t>bool</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
     <t>ID</t>
+  </si>
+  <si>
+    <t>是否导出到代码中</t>
   </si>
   <si>
     <t>简体中文</t>
@@ -177,6 +186,74 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -186,21 +263,30 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -214,99 +300,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="等线"/>
@@ -329,181 +338,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -532,76 +541,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -624,8 +568,73 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -637,10 +646,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -649,137 +658,137 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -789,11 +798,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="31" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1114,218 +1129,243 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
     <col min="2" max="2" width="16.125" style="2" customWidth="1"/>
     <col min="3" max="3" width="25.5" style="2" customWidth="1"/>
-    <col min="4" max="4" width="31.75" style="2" customWidth="1"/>
-    <col min="5" max="5" width="33.375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="29" style="2" customWidth="1"/>
-    <col min="7" max="7" width="24.875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="19.25" style="2" customWidth="1"/>
-    <col min="9" max="9" width="14.625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="12.25" style="2" customWidth="1"/>
-    <col min="11" max="11" width="12.75" style="2" customWidth="1"/>
-    <col min="12" max="14" width="9" style="2"/>
-    <col min="15" max="15" width="18.125" style="2" customWidth="1"/>
-    <col min="16" max="17" width="11.75" style="2" customWidth="1"/>
+    <col min="4" max="4" width="16.125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="31.75" style="2" customWidth="1"/>
+    <col min="6" max="6" width="33.375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="29" style="2" customWidth="1"/>
+    <col min="8" max="8" width="24.875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="19.25" style="2" customWidth="1"/>
+    <col min="10" max="10" width="14.625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="12.25" style="2" customWidth="1"/>
+    <col min="12" max="12" width="12.75" style="2" customWidth="1"/>
+    <col min="13" max="15" width="9" style="2"/>
+    <col min="16" max="16" width="18.125" style="2" customWidth="1"/>
+    <col min="17" max="18" width="11.75" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:17">
-      <c r="A1" s="3" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:18">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="4" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:17">
-      <c r="A2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3" t="s">
+    <row r="2" s="1" customFormat="1" spans="1:18">
+      <c r="A2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>18</v>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:17">
-      <c r="A3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="3" t="s">
+    <row r="3" s="1" customFormat="1" spans="1:18">
+      <c r="A3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="J3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="K3" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="L3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="M3" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="N3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="O3" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="P3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="4" spans="3:4">
-      <c r="C4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>36</v>
+    <row r="4" spans="3:5">
+      <c r="C4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="5" spans="3:4">
-      <c r="C5" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>38</v>
+    <row r="5" spans="3:5">
+      <c r="C5" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="6" ht="28.5" spans="3:4">
-      <c r="C6" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>40</v>
+    <row r="6" ht="28.5" spans="3:5">
+      <c r="C6" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="7" ht="28.5" spans="3:4">
-      <c r="C7" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>42</v>
+    <row r="7" ht="28.5" spans="3:5">
+      <c r="C7" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="8" spans="3:4">
-      <c r="C8" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>44</v>
+    <row r="8" spans="3:5">
+      <c r="C8" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
